--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/146.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/146.xlsx
@@ -426,13 +426,13 @@
         <v>-2.302174502142055</v>
       </c>
       <c r="E2">
-        <v>-20.07410242329724</v>
+        <v>-18.1510180088299</v>
       </c>
       <c r="F2">
-        <v>1.349281954965453</v>
+        <v>1.196415034452832</v>
       </c>
       <c r="G2">
-        <v>-10.70252147111997</v>
+        <v>-9.064284768829461</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.043979971923316</v>
       </c>
       <c r="E3">
-        <v>-19.32475771535199</v>
+        <v>-18.39925536850837</v>
       </c>
       <c r="F3">
-        <v>0.8913886191895815</v>
+        <v>1.929379363471919</v>
       </c>
       <c r="G3">
-        <v>-9.819678428889283</v>
+        <v>-7.532700601632119</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.702508454373179</v>
       </c>
       <c r="E4">
-        <v>-20.4006778548344</v>
+        <v>-18.76293258759037</v>
       </c>
       <c r="F4">
-        <v>1.563761186163495</v>
+        <v>1.499903999816487</v>
       </c>
       <c r="G4">
-        <v>-10.38628160848109</v>
+        <v>-8.643233034417255</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.299564556128826</v>
       </c>
       <c r="E5">
-        <v>-20.98501855536215</v>
+        <v>-18.86445191789432</v>
       </c>
       <c r="F5">
-        <v>1.499261186711915</v>
+        <v>2.017441445328728</v>
       </c>
       <c r="G5">
-        <v>-10.72081223522444</v>
+        <v>-7.729462875758702</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.8425931812539301</v>
       </c>
       <c r="E6">
-        <v>-20.96302828558091</v>
+        <v>-19.41164101766316</v>
       </c>
       <c r="F6">
-        <v>1.11382349092411</v>
+        <v>1.73308114003052</v>
       </c>
       <c r="G6">
-        <v>-10.98323918012247</v>
+        <v>-8.28023502658171</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.3453560012057033</v>
       </c>
       <c r="E7">
-        <v>-22.6205312849204</v>
+        <v>-18.965808223134</v>
       </c>
       <c r="F7">
-        <v>1.223958250595916</v>
+        <v>2.05904205629732</v>
       </c>
       <c r="G7">
-        <v>-10.68653815725636</v>
+        <v>-7.512128871651087</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.1799469893799279</v>
       </c>
       <c r="E8">
-        <v>-23.61061872806141</v>
+        <v>-21.6962833253769</v>
       </c>
       <c r="F8">
-        <v>1.298716751963765</v>
+        <v>1.6223797770552</v>
       </c>
       <c r="G8">
-        <v>-9.131760308010888</v>
+        <v>-7.83480443481831</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.7197352785877571</v>
       </c>
       <c r="E9">
-        <v>-22.55379969194336</v>
+        <v>-21.75020839386024</v>
       </c>
       <c r="F9">
-        <v>1.259488585236792</v>
+        <v>1.738445647331049</v>
       </c>
       <c r="G9">
-        <v>-9.217718622938063</v>
+        <v>-6.435532841189019</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.262917525225226</v>
       </c>
       <c r="E10">
-        <v>-22.80953167610453</v>
+        <v>-24.15233743122898</v>
       </c>
       <c r="F10">
-        <v>2.119077155447811</v>
+        <v>1.616324411340735</v>
       </c>
       <c r="G10">
-        <v>-9.537245857297441</v>
+        <v>-6.846335126611641</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.798342498169333</v>
       </c>
       <c r="E11">
-        <v>-23.44319651552383</v>
+        <v>-22.89119817635885</v>
       </c>
       <c r="F11">
-        <v>2.091673105028398</v>
+        <v>2.05649731163592</v>
       </c>
       <c r="G11">
-        <v>-8.89304349026512</v>
+        <v>-7.414431362241655</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.315025699342706</v>
       </c>
       <c r="E12">
-        <v>-25.69417414746455</v>
+        <v>-22.72006714360899</v>
       </c>
       <c r="F12">
-        <v>2.186214676709906</v>
+        <v>2.086933186749579</v>
       </c>
       <c r="G12">
-        <v>-8.711052870334765</v>
+        <v>-6.409624511798683</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.8094301161073</v>
       </c>
       <c r="E13">
-        <v>-24.75798007348882</v>
+        <v>-24.28592741445526</v>
       </c>
       <c r="F13">
-        <v>2.335604110865574</v>
+        <v>2.395215085905832</v>
       </c>
       <c r="G13">
-        <v>-8.489451573027031</v>
+        <v>-5.60831689565471</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.276399391309303</v>
       </c>
       <c r="E14">
-        <v>-25.92566521026265</v>
+        <v>-24.94271011368372</v>
       </c>
       <c r="F14">
-        <v>2.684694701753342</v>
+        <v>2.302497579245289</v>
       </c>
       <c r="G14">
-        <v>-8.298198046677795</v>
+        <v>-5.540742040107106</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.713905964504479</v>
       </c>
       <c r="E15">
-        <v>-26.6974439784419</v>
+        <v>-26.4849045793659</v>
       </c>
       <c r="F15">
-        <v>2.237848473661204</v>
+        <v>2.652892020425063</v>
       </c>
       <c r="G15">
-        <v>-7.293470649327765</v>
+        <v>-5.549620923243431</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.121303715327969</v>
       </c>
       <c r="E16">
-        <v>-27.38453122572969</v>
+        <v>-26.29640684879661</v>
       </c>
       <c r="F16">
-        <v>2.768278629430617</v>
+        <v>3.056880175831159</v>
       </c>
       <c r="G16">
-        <v>-7.878069954471046</v>
+        <v>-2.802573271848211</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.498976211228501</v>
       </c>
       <c r="E17">
-        <v>-28.76274511912012</v>
+        <v>-27.341614877559</v>
       </c>
       <c r="F17">
-        <v>2.735226770058917</v>
+        <v>2.830540380159834</v>
       </c>
       <c r="G17">
-        <v>-7.257206933490588</v>
+        <v>-3.642392464250526</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.845884533176038</v>
       </c>
       <c r="E18">
-        <v>-28.27423145706867</v>
+        <v>-29.39095314736018</v>
       </c>
       <c r="F18">
-        <v>2.859574657627956</v>
+        <v>3.488214395938473</v>
       </c>
       <c r="G18">
-        <v>-6.319945143685366</v>
+        <v>-3.927956811922519</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.164733324262034</v>
       </c>
       <c r="E19">
-        <v>-29.2734800031272</v>
+        <v>-28.01114975959306</v>
       </c>
       <c r="F19">
-        <v>3.070168845706869</v>
+        <v>3.136582373858916</v>
       </c>
       <c r="G19">
-        <v>-5.412190246271666</v>
+        <v>-3.06971443359416</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.458804994879076</v>
       </c>
       <c r="E20">
-        <v>-30.12708829662505</v>
+        <v>-27.40578335424768</v>
       </c>
       <c r="F20">
-        <v>2.951052926653912</v>
+        <v>3.188474621439889</v>
       </c>
       <c r="G20">
-        <v>-4.729320707340659</v>
+        <v>-3.430401680643295</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.730625772668985</v>
       </c>
       <c r="E21">
-        <v>-28.51327148603756</v>
+        <v>-27.60734120385509</v>
       </c>
       <c r="F21">
-        <v>3.051954703254113</v>
+        <v>3.323304670123953</v>
       </c>
       <c r="G21">
-        <v>-5.166448450891566</v>
+        <v>-3.377479299652506</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.981375639450192</v>
       </c>
       <c r="E22">
-        <v>-30.28625962952065</v>
+        <v>-30.18762946563359</v>
       </c>
       <c r="F22">
-        <v>3.711699637539752</v>
+        <v>3.627698212691465</v>
       </c>
       <c r="G22">
-        <v>-5.290895168258309</v>
+        <v>-2.491017831147399</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.210884142156897</v>
       </c>
       <c r="E23">
-        <v>-30.860318429814</v>
+        <v>-29.57083772036687</v>
       </c>
       <c r="F23">
-        <v>3.892676377498971</v>
+        <v>3.558547758640568</v>
       </c>
       <c r="G23">
-        <v>-5.053611816731047</v>
+        <v>-1.86939007414737</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.416027226648906</v>
       </c>
       <c r="E24">
-        <v>-31.9257279811246</v>
+        <v>-30.60489891035937</v>
       </c>
       <c r="F24">
-        <v>4.139667372522088</v>
+        <v>3.585870629054507</v>
       </c>
       <c r="G24">
-        <v>-4.181749854054127</v>
+        <v>-2.640853122254813</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.592557426680941</v>
       </c>
       <c r="E25">
-        <v>-31.91313655914627</v>
+        <v>-31.90343883205884</v>
       </c>
       <c r="F25">
-        <v>3.891173719030293</v>
+        <v>3.832150884846022</v>
       </c>
       <c r="G25">
-        <v>-4.465735071503888</v>
+        <v>-2.448947418434341</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.739503187960991</v>
       </c>
       <c r="E26">
-        <v>-31.38929627136098</v>
+        <v>-31.47593050760172</v>
       </c>
       <c r="F26">
-        <v>3.780155919707103</v>
+        <v>3.635910647122819</v>
       </c>
       <c r="G26">
-        <v>-4.873564487032244</v>
+        <v>-1.770997350174691</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.856683990148538</v>
       </c>
       <c r="E27">
-        <v>-32.90952084539495</v>
+        <v>-30.30141190355032</v>
       </c>
       <c r="F27">
-        <v>3.593595983453015</v>
+        <v>4.46683604846217</v>
       </c>
       <c r="G27">
-        <v>-3.781445308536533</v>
+        <v>-2.313337541509175</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.944133051100266</v>
       </c>
       <c r="E28">
-        <v>-33.03517467792278</v>
+        <v>-32.52342088726397</v>
       </c>
       <c r="F28">
-        <v>4.554555186214221</v>
+        <v>3.890718116958753</v>
       </c>
       <c r="G28">
-        <v>-4.530926334263215</v>
+        <v>-3.007307339633359</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.003257769725417</v>
       </c>
       <c r="E29">
-        <v>-34.01579761038777</v>
+        <v>-32.21925687359077</v>
       </c>
       <c r="F29">
-        <v>3.807743867689938</v>
+        <v>4.224558463960982</v>
       </c>
       <c r="G29">
-        <v>-3.571973850084688</v>
+        <v>-3.630937976684647</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>7.036930470381043</v>
       </c>
       <c r="E30">
-        <v>-32.29097205221325</v>
+        <v>-30.9803456333873</v>
       </c>
       <c r="F30">
-        <v>3.77555682388676</v>
+        <v>4.36811287813133</v>
       </c>
       <c r="G30">
-        <v>-6.132545092343841</v>
+        <v>-2.734160848279171</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>7.046545367717706</v>
       </c>
       <c r="E31">
-        <v>-33.07847594638412</v>
+        <v>-31.94823223270571</v>
       </c>
       <c r="F31">
-        <v>4.392057666276653</v>
+        <v>3.687600773057508</v>
       </c>
       <c r="G31">
-        <v>-5.239217552390286</v>
+        <v>-2.366862441788112</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>7.038455765396448</v>
       </c>
       <c r="E32">
-        <v>-32.59329976967634</v>
+        <v>-31.78710459903879</v>
       </c>
       <c r="F32">
-        <v>4.343086242157952</v>
+        <v>4.230794413769257</v>
       </c>
       <c r="G32">
-        <v>-5.326572917535035</v>
+        <v>-2.619738462805342</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>7.02201146739417</v>
       </c>
       <c r="E33">
-        <v>-33.15635437813103</v>
+        <v>-31.7934852189156</v>
       </c>
       <c r="F33">
-        <v>4.153883813888934</v>
+        <v>4.472740651309325</v>
       </c>
       <c r="G33">
-        <v>-5.268108683311506</v>
+        <v>-3.342702018762462</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>7.00304701556334</v>
       </c>
       <c r="E34">
-        <v>-32.5559692941941</v>
+        <v>-30.28658567964921</v>
       </c>
       <c r="F34">
-        <v>4.102717216152814</v>
+        <v>4.484236734125377</v>
       </c>
       <c r="G34">
-        <v>-4.217318355328056</v>
+        <v>-1.506392066311824</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.985854350351746</v>
       </c>
       <c r="E35">
-        <v>-31.72619209516162</v>
+        <v>-30.47890997075497</v>
       </c>
       <c r="F35">
-        <v>4.022443444617124</v>
+        <v>4.001586810149439</v>
       </c>
       <c r="G35">
-        <v>-4.656376146928358</v>
+        <v>-2.613762928106957</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.972495090054845</v>
       </c>
       <c r="E36">
-        <v>-31.4133334113937</v>
+        <v>-30.67608199328594</v>
       </c>
       <c r="F36">
-        <v>4.118399867822614</v>
+        <v>4.517571895148834</v>
       </c>
       <c r="G36">
-        <v>-5.696145668811574</v>
+        <v>-2.934935503599351</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.959896808554374</v>
       </c>
       <c r="E37">
-        <v>-32.76178617360571</v>
+        <v>-28.83068581465719</v>
       </c>
       <c r="F37">
-        <v>4.106352092316298</v>
+        <v>3.724057222454715</v>
       </c>
       <c r="G37">
-        <v>-5.390228087164141</v>
+        <v>-2.910126275328053</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.944702365995303</v>
       </c>
       <c r="E38">
-        <v>-30.6027931699458</v>
+        <v>-30.54375771854481</v>
       </c>
       <c r="F38">
-        <v>4.443585432200393</v>
+        <v>3.826254565672896</v>
       </c>
       <c r="G38">
-        <v>-6.254674427833095</v>
+        <v>-3.511533220174214</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>6.925453162875951</v>
       </c>
       <c r="E39">
-        <v>-30.06355154206043</v>
+        <v>-29.93401680730802</v>
       </c>
       <c r="F39">
-        <v>4.056303790573957</v>
+        <v>4.195590455885083</v>
       </c>
       <c r="G39">
-        <v>-5.75825812421938</v>
+        <v>-3.628259745343377</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>6.897567276052314</v>
       </c>
       <c r="E40">
-        <v>-31.85141798689573</v>
+        <v>-28.6863407056627</v>
       </c>
       <c r="F40">
-        <v>3.880119984407336</v>
+        <v>4.068477477925499</v>
       </c>
       <c r="G40">
-        <v>-6.90884153693862</v>
+        <v>-3.171470671834738</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>6.855204873476238</v>
       </c>
       <c r="E41">
-        <v>-29.98928230409763</v>
+        <v>-30.7361023877836</v>
       </c>
       <c r="F41">
-        <v>4.077321128317786</v>
+        <v>3.647696658529851</v>
       </c>
       <c r="G41">
-        <v>-6.163631114957598</v>
+        <v>-3.777813640079953</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>6.792870713718656</v>
       </c>
       <c r="E42">
-        <v>-30.32212740789841</v>
+        <v>-27.80911642021485</v>
       </c>
       <c r="F42">
-        <v>4.268137216287458</v>
+        <v>4.260729954971625</v>
       </c>
       <c r="G42">
-        <v>-6.087385940642643</v>
+        <v>-4.219082876100487</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.705106503431852</v>
       </c>
       <c r="E43">
-        <v>-27.96616389880086</v>
+        <v>-26.75649075102791</v>
       </c>
       <c r="F43">
-        <v>4.456178273457751</v>
+        <v>3.904396119513779</v>
       </c>
       <c r="G43">
-        <v>-6.510149227098652</v>
+        <v>-2.723666418919682</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.587457208123039</v>
       </c>
       <c r="E44">
-        <v>-27.88856849667943</v>
+        <v>-26.68189772717356</v>
       </c>
       <c r="F44">
-        <v>4.446125206657377</v>
+        <v>4.595077262824367</v>
       </c>
       <c r="G44">
-        <v>-6.407095255006679</v>
+        <v>-2.922981123657043</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.440494288947493</v>
       </c>
       <c r="E45">
-        <v>-28.27227062782335</v>
+        <v>-27.03573004376289</v>
       </c>
       <c r="F45">
-        <v>4.876573073643695</v>
+        <v>4.59595698900614</v>
       </c>
       <c r="G45">
-        <v>-6.659891822930966</v>
+        <v>-3.581359246688522</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.266561993007936</v>
       </c>
       <c r="E46">
-        <v>-28.67939855500894</v>
+        <v>-25.55118758067236</v>
       </c>
       <c r="F46">
-        <v>4.640950592856598</v>
+        <v>4.543214836469896</v>
       </c>
       <c r="G46">
-        <v>-6.683979352274704</v>
+        <v>-3.553289131061041</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.066823079083345</v>
       </c>
       <c r="E47">
-        <v>-29.29417512934225</v>
+        <v>-26.88724138105137</v>
       </c>
       <c r="F47">
-        <v>4.686767593905438</v>
+        <v>4.315327650490141</v>
       </c>
       <c r="G47">
-        <v>-7.218347749950623</v>
+        <v>-3.156364652539044</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.842906424022352</v>
       </c>
       <c r="E48">
-        <v>-27.20125482569125</v>
+        <v>-25.42881915603709</v>
       </c>
       <c r="F48">
-        <v>4.143444727878854</v>
+        <v>4.813736435936936</v>
       </c>
       <c r="G48">
-        <v>-7.333597771809271</v>
+        <v>-5.046414690728671</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.596257333385495</v>
       </c>
       <c r="E49">
-        <v>-27.1051696641965</v>
+        <v>-23.86486537274806</v>
       </c>
       <c r="F49">
-        <v>4.39188536585687</v>
+        <v>4.858846011223785</v>
       </c>
       <c r="G49">
-        <v>-7.641836045879733</v>
+        <v>-3.219364334151375</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.327433280468891</v>
       </c>
       <c r="E50">
-        <v>-27.21425607456727</v>
+        <v>-25.23023651385273</v>
       </c>
       <c r="F50">
-        <v>4.562326929187286</v>
+        <v>4.521553028886689</v>
       </c>
       <c r="G50">
-        <v>-7.595097763956302</v>
+        <v>-4.55057442203879</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.037673894004388</v>
       </c>
       <c r="E51">
-        <v>-27.37948650568514</v>
+        <v>-23.88142600219411</v>
       </c>
       <c r="F51">
-        <v>4.31430378838028</v>
+        <v>4.398739277747634</v>
       </c>
       <c r="G51">
-        <v>-7.552547322140049</v>
+        <v>-3.971983757049286</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.731890933702973</v>
       </c>
       <c r="E52">
-        <v>-25.39956974242155</v>
+        <v>-22.18196216269954</v>
       </c>
       <c r="F52">
-        <v>4.884816986036356</v>
+        <v>4.534278408928494</v>
       </c>
       <c r="G52">
-        <v>-7.618357656915221</v>
+        <v>-5.936378716414327</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.411994367246823</v>
       </c>
       <c r="E53">
-        <v>-23.74568046534018</v>
+        <v>-23.40171116513956</v>
       </c>
       <c r="F53">
-        <v>4.505437969432627</v>
+        <v>4.728994450630546</v>
       </c>
       <c r="G53">
-        <v>-7.913668250654829</v>
+        <v>-4.960459686347034</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.080108662677071</v>
       </c>
       <c r="E54">
-        <v>-24.43276318415397</v>
+        <v>-22.66149586079378</v>
       </c>
       <c r="F54">
-        <v>4.755604925078077</v>
+        <v>4.451019201273116</v>
       </c>
       <c r="G54">
-        <v>-9.245004139272737</v>
+        <v>-6.25287680160527</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.738981953813477</v>
       </c>
       <c r="E55">
-        <v>-23.82971535750052</v>
+        <v>-22.19676121575661</v>
       </c>
       <c r="F55">
-        <v>4.72762267421151</v>
+        <v>5.546258416762927</v>
       </c>
       <c r="G55">
-        <v>-9.37376780802269</v>
+        <v>-5.898175020891138</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.391874390289158</v>
       </c>
       <c r="E56">
-        <v>-25.1091270049916</v>
+        <v>-21.04708129163728</v>
       </c>
       <c r="F56">
-        <v>4.245007541666491</v>
+        <v>4.392632553254196</v>
       </c>
       <c r="G56">
-        <v>-8.049503244676664</v>
+        <v>-6.972152409831643</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.04159806369077</v>
       </c>
       <c r="E57">
-        <v>-23.97652848482919</v>
+        <v>-22.08247611722503</v>
       </c>
       <c r="F57">
-        <v>4.216669092816719</v>
+        <v>4.81904627098888</v>
       </c>
       <c r="G57">
-        <v>-8.582851994326489</v>
+        <v>-6.063602981488518</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.695627405677309</v>
       </c>
       <c r="E58">
-        <v>-22.33200862046969</v>
+        <v>-20.27911097009848</v>
       </c>
       <c r="F58">
-        <v>4.059738201825964</v>
+        <v>5.141788151528401</v>
       </c>
       <c r="G58">
-        <v>-8.792283726231863</v>
+        <v>-6.545903118922781</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.359231774297553</v>
       </c>
       <c r="E59">
-        <v>-23.81386569847367</v>
+        <v>-20.6982348249304</v>
       </c>
       <c r="F59">
-        <v>4.125394602171853</v>
+        <v>4.339400007215494</v>
       </c>
       <c r="G59">
-        <v>-7.941887340831577</v>
+        <v>-6.429107072297294</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.036548436749889</v>
       </c>
       <c r="E60">
-        <v>-22.92858978624019</v>
+        <v>-19.7940027205008</v>
       </c>
       <c r="F60">
-        <v>4.284856983945564</v>
+        <v>4.778245862931394</v>
       </c>
       <c r="G60">
-        <v>-9.292123133933183</v>
+        <v>-6.9021211294939</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.73099273482868</v>
       </c>
       <c r="E61">
-        <v>-22.77180948762063</v>
+        <v>-18.57696627399138</v>
       </c>
       <c r="F61">
-        <v>4.161960396066228</v>
+        <v>4.573794847511643</v>
       </c>
       <c r="G61">
-        <v>-9.852072116991051</v>
+        <v>-7.272607591339278</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.445428567030461</v>
       </c>
       <c r="E62">
-        <v>-23.34823441558298</v>
+        <v>-20.20091328093403</v>
       </c>
       <c r="F62">
-        <v>4.152508724000286</v>
+        <v>4.946942884511513</v>
       </c>
       <c r="G62">
-        <v>-10.22236987774069</v>
+        <v>-7.570950644792858</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.181110471697694</v>
       </c>
       <c r="E63">
-        <v>-19.6354246177002</v>
+        <v>-20.00448619237732</v>
       </c>
       <c r="F63">
-        <v>3.407940624402784</v>
+        <v>4.449042716650037</v>
       </c>
       <c r="G63">
-        <v>-9.855991802909548</v>
+        <v>-6.966921747879594</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.9404283878212238</v>
       </c>
       <c r="E64">
-        <v>-21.10453404137259</v>
+        <v>-19.32838049455813</v>
       </c>
       <c r="F64">
-        <v>3.674186191336573</v>
+        <v>4.320881025558508</v>
       </c>
       <c r="G64">
-        <v>-9.865555968972503</v>
+        <v>-6.97316212622112</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.725398054282146</v>
       </c>
       <c r="E65">
-        <v>-20.04281519637824</v>
+        <v>-18.98119144933806</v>
       </c>
       <c r="F65">
-        <v>4.257643458028794</v>
+        <v>4.819669203275786</v>
       </c>
       <c r="G65">
-        <v>-10.01952282091293</v>
+        <v>-7.935415224302301</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.5360111131546379</v>
       </c>
       <c r="E66">
-        <v>-22.29595743889463</v>
+        <v>-21.30150907528423</v>
       </c>
       <c r="F66">
-        <v>3.633730384118651</v>
+        <v>4.207795621197931</v>
       </c>
       <c r="G66">
-        <v>-10.4770567671679</v>
+        <v>-7.612415227672229</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.3717210833870509</v>
       </c>
       <c r="E67">
-        <v>-21.53966605182162</v>
+        <v>-18.87344999574757</v>
       </c>
       <c r="F67">
-        <v>3.356745862174969</v>
+        <v>3.660779893289666</v>
       </c>
       <c r="G67">
-        <v>-8.959409996690891</v>
+        <v>-6.657319529046952</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.23137646183233</v>
       </c>
       <c r="E68">
-        <v>-21.26571148825359</v>
+        <v>-19.71439214744596</v>
       </c>
       <c r="F68">
-        <v>3.300935436778755</v>
+        <v>4.49521260221247</v>
       </c>
       <c r="G68">
-        <v>-9.208144525238492</v>
+        <v>-8.106318827221637</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.1131574469356987</v>
       </c>
       <c r="E69">
-        <v>-19.74759039039619</v>
+        <v>-18.17590197350205</v>
       </c>
       <c r="F69">
-        <v>3.313177050257326</v>
+        <v>4.111239459992815</v>
       </c>
       <c r="G69">
-        <v>-10.6744778398568</v>
+        <v>-6.984513986875281</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.01485424590113144</v>
       </c>
       <c r="E70">
-        <v>-21.38845124775749</v>
+        <v>-19.5569008784072</v>
       </c>
       <c r="F70">
-        <v>2.729544169675712</v>
+        <v>4.61168105904608</v>
       </c>
       <c r="G70">
-        <v>-9.935577317673628</v>
+        <v>-6.769523849009471</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.06441316858945469</v>
       </c>
       <c r="E71">
-        <v>-21.29299554414981</v>
+        <v>-18.5482285779387</v>
       </c>
       <c r="F71">
-        <v>3.217581795239458</v>
+        <v>4.418820560326299</v>
       </c>
       <c r="G71">
-        <v>-9.969881190551556</v>
+        <v>-8.17407907331944</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.1265998675161626</v>
       </c>
       <c r="E72">
-        <v>-20.94776279970105</v>
+        <v>-18.15104970814796</v>
       </c>
       <c r="F72">
-        <v>3.700380825347899</v>
+        <v>4.149566362985542</v>
       </c>
       <c r="G72">
-        <v>-10.23441033186702</v>
+        <v>-7.607492446455333</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.173305766159204</v>
       </c>
       <c r="E73">
-        <v>-21.04540575625444</v>
+        <v>-19.4584246826364</v>
       </c>
       <c r="F73">
-        <v>2.972655091784117</v>
+        <v>3.958604482352978</v>
       </c>
       <c r="G73">
-        <v>-9.152997457645311</v>
+        <v>-7.929621769608577</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.20585601361655</v>
       </c>
       <c r="E74">
-        <v>-18.94371832692459</v>
+        <v>-19.09677169143583</v>
       </c>
       <c r="F74">
-        <v>3.018274941391091</v>
+        <v>3.639240684082074</v>
       </c>
       <c r="G74">
-        <v>-9.511999637014958</v>
+        <v>-8.299118378337713</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.2253651594201292</v>
       </c>
       <c r="E75">
-        <v>-22.08163382105961</v>
+        <v>-17.78100998308518</v>
       </c>
       <c r="F75">
-        <v>3.015219922409567</v>
+        <v>3.806408539436625</v>
       </c>
       <c r="G75">
-        <v>-10.26059674708265</v>
+        <v>-7.610922171634018</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.2324726794564133</v>
       </c>
       <c r="E76">
-        <v>-19.9523996843411</v>
+        <v>-20.23061554195034</v>
       </c>
       <c r="F76">
-        <v>2.556518100048563</v>
+        <v>3.352499650868219</v>
       </c>
       <c r="G76">
-        <v>-9.823124706795664</v>
+        <v>-7.82290633415017</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.2268576356108212</v>
       </c>
       <c r="E77">
-        <v>-21.22097469353182</v>
+        <v>-19.61276413376582</v>
       </c>
       <c r="F77">
-        <v>2.613324223062942</v>
+        <v>3.049800948006835</v>
       </c>
       <c r="G77">
-        <v>-9.109652484899634</v>
+        <v>-9.303153871670036</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.2082370746161567</v>
       </c>
       <c r="E78">
-        <v>-23.12946836474644</v>
+        <v>-19.53245617571379</v>
       </c>
       <c r="F78">
-        <v>2.460574930721518</v>
+        <v>3.545242521416802</v>
       </c>
       <c r="G78">
-        <v>-8.637442890269071</v>
+        <v>-8.17385395622277</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.1759956017184907</v>
       </c>
       <c r="E79">
-        <v>-21.81126128043165</v>
+        <v>-18.96872456039494</v>
       </c>
       <c r="F79">
-        <v>2.483292078375892</v>
+        <v>3.275395213015641</v>
       </c>
       <c r="G79">
-        <v>-8.646285357404464</v>
+        <v>-5.955745407819063</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.1295892004725206</v>
       </c>
       <c r="E80">
-        <v>-21.98528600807241</v>
+        <v>-20.16471265971671</v>
       </c>
       <c r="F80">
-        <v>2.572571860314817</v>
+        <v>3.498272432943265</v>
       </c>
       <c r="G80">
-        <v>-9.363889140133505</v>
+        <v>-6.140675792188291</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.0691208992536765</v>
       </c>
       <c r="E81">
-        <v>-23.70905869604015</v>
+        <v>-20.54876348335922</v>
       </c>
       <c r="F81">
-        <v>3.124764884490579</v>
+        <v>3.478418123032966</v>
       </c>
       <c r="G81">
-        <v>-9.323341578368511</v>
+        <v>-7.885478955387935</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.005008584593991776</v>
       </c>
       <c r="E82">
-        <v>-24.16748517678463</v>
+        <v>-22.06955185240714</v>
       </c>
       <c r="F82">
-        <v>2.333935778916336</v>
+        <v>3.59486669904891</v>
       </c>
       <c r="G82">
-        <v>-8.051552472365474</v>
+        <v>-7.853234241835433</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.09196781625994563</v>
       </c>
       <c r="E83">
-        <v>-24.440461589967</v>
+        <v>-22.09325388536329</v>
       </c>
       <c r="F83">
-        <v>2.705895937060592</v>
+        <v>2.865079987386962</v>
       </c>
       <c r="G83">
-        <v>-8.497820632150308</v>
+        <v>-6.965968310764284</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.190159427234736</v>
       </c>
       <c r="E84">
-        <v>-25.33225850477153</v>
+        <v>-24.43672559891068</v>
       </c>
       <c r="F84">
-        <v>2.681719206042486</v>
+        <v>3.115008373220406</v>
       </c>
       <c r="G84">
-        <v>-7.927128928817505</v>
+        <v>-6.999212809069645</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.2978389451004362</v>
       </c>
       <c r="E85">
-        <v>-25.36583713953841</v>
+        <v>-25.00478190690685</v>
       </c>
       <c r="F85">
-        <v>2.45391485680301</v>
+        <v>3.350589435637363</v>
       </c>
       <c r="G85">
-        <v>-7.841243445892193</v>
+        <v>-7.604486471105675</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.4131602193838059</v>
       </c>
       <c r="E86">
-        <v>-27.64259990247881</v>
+        <v>-24.94458490192289</v>
       </c>
       <c r="F86">
-        <v>2.57443403023631</v>
+        <v>3.371596832972359</v>
       </c>
       <c r="G86">
-        <v>-8.458550940963473</v>
+        <v>-7.085101602540496</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.534010538924004</v>
       </c>
       <c r="E87">
-        <v>-28.15279136960497</v>
+        <v>-25.31870931054059</v>
       </c>
       <c r="F87">
-        <v>2.962560606613602</v>
+        <v>3.548758112674284</v>
       </c>
       <c r="G87">
-        <v>-8.270270284508504</v>
+        <v>-6.193128075712504</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.6581730324859667</v>
       </c>
       <c r="E88">
-        <v>-28.81472294378015</v>
+        <v>-26.65613071006992</v>
       </c>
       <c r="F88">
-        <v>2.581127238850931</v>
+        <v>3.730120871843207</v>
       </c>
       <c r="G88">
-        <v>-8.769169497276671</v>
+        <v>-6.429156730480383</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.7844927812057663</v>
       </c>
       <c r="E89">
-        <v>-30.3099616624768</v>
+        <v>-28.80065750351233</v>
       </c>
       <c r="F89">
-        <v>2.7403112891773</v>
+        <v>3.304451028036237</v>
       </c>
       <c r="G89">
-        <v>-8.344856875508283</v>
+        <v>-6.902154234949292</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.9117493347995321</v>
       </c>
       <c r="E90">
-        <v>-31.94827978168279</v>
+        <v>-30.43066360867725</v>
       </c>
       <c r="F90">
-        <v>2.93232519641142</v>
+        <v>3.268345806417817</v>
       </c>
       <c r="G90">
-        <v>-8.463814708370915</v>
+        <v>-5.845444651541626</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.038960540697655</v>
       </c>
       <c r="E91">
-        <v>-33.04771628668703</v>
+        <v>-31.53490256036661</v>
       </c>
       <c r="F91">
-        <v>2.530659783202773</v>
+        <v>3.190335134626577</v>
       </c>
       <c r="G91">
-        <v>-7.140877673786138</v>
+        <v>-5.551031215643161</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.16536175169525</v>
       </c>
       <c r="E92">
-        <v>-33.93870486888119</v>
+        <v>-33.28756464826628</v>
       </c>
       <c r="F92">
-        <v>2.60704188468011</v>
+        <v>3.237361552083505</v>
       </c>
       <c r="G92">
-        <v>-8.637800429187312</v>
+        <v>-6.238436201962969</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.289966404023794</v>
       </c>
       <c r="E93">
-        <v>-35.56737733845085</v>
+        <v>-34.02298656287495</v>
       </c>
       <c r="F93">
-        <v>2.871141980040649</v>
+        <v>2.889601319244633</v>
       </c>
       <c r="G93">
-        <v>-7.693758642117662</v>
+        <v>-5.093245667927202</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.410684319310161</v>
       </c>
       <c r="E94">
-        <v>-37.4018598947211</v>
+        <v>-36.63923317251136</v>
       </c>
       <c r="F94">
-        <v>2.473805614879032</v>
+        <v>2.90201357640818</v>
       </c>
       <c r="G94">
-        <v>-8.210928755717067</v>
+        <v>-4.954722510927478</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.526923782864233</v>
       </c>
       <c r="E95">
-        <v>-39.44891128514841</v>
+        <v>-39.18980332361453</v>
       </c>
       <c r="F95">
-        <v>2.46328866233309</v>
+        <v>2.939608202616833</v>
       </c>
       <c r="G95">
-        <v>-8.251724608397506</v>
+        <v>-6.489368932748647</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.637316499483593</v>
       </c>
       <c r="E96">
-        <v>-42.29311221938293</v>
+        <v>-40.24652726177842</v>
       </c>
       <c r="F96">
-        <v>2.373369380759204</v>
+        <v>2.710899276173501</v>
       </c>
       <c r="G96">
-        <v>-7.782176692380516</v>
+        <v>-6.059574047567225</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.740465503126297</v>
       </c>
       <c r="E97">
-        <v>-42.18120456970539</v>
+        <v>-42.28680179085325</v>
       </c>
       <c r="F97">
-        <v>3.217568541361013</v>
+        <v>3.273059216939747</v>
       </c>
       <c r="G97">
-        <v>-8.162336568291645</v>
+        <v>-5.63665847601641</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.834997044775719</v>
       </c>
       <c r="E98">
-        <v>-46.18979617587316</v>
+        <v>-44.45522534163413</v>
       </c>
       <c r="F98">
-        <v>2.509037737254901</v>
+        <v>2.698970785573188</v>
       </c>
       <c r="G98">
-        <v>-8.969417775856106</v>
+        <v>-5.750441926201161</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.920126555938451</v>
       </c>
       <c r="E99">
-        <v>-46.13730210517625</v>
+        <v>-45.68732349269307</v>
       </c>
       <c r="F99">
-        <v>2.824952213660548</v>
+        <v>2.278325818431599</v>
       </c>
       <c r="G99">
-        <v>-8.005813975194902</v>
+        <v>-4.781614084678987</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.994366657259026</v>
       </c>
       <c r="E100">
-        <v>-48.95399029557717</v>
+        <v>-47.48219322258123</v>
       </c>
       <c r="F100">
-        <v>2.834046031008481</v>
+        <v>2.619444201434824</v>
       </c>
       <c r="G100">
-        <v>-8.251158505110292</v>
+        <v>-6.28022521830519</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.057617368920227</v>
       </c>
       <c r="E101">
-        <v>-50.87384477595853</v>
+        <v>-49.46217451659944</v>
       </c>
       <c r="F101">
-        <v>2.340602479774066</v>
+        <v>2.070629259527679</v>
       </c>
       <c r="G101">
-        <v>-8.071382640145709</v>
+        <v>-5.195998380375101</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.110110286287037</v>
       </c>
       <c r="E102">
-        <v>-52.48378294855846</v>
+        <v>-50.36035771187328</v>
       </c>
       <c r="F102">
-        <v>2.515235582162647</v>
+        <v>1.671950939173528</v>
       </c>
       <c r="G102">
-        <v>-8.574549146113997</v>
+        <v>-5.755182627413397</v>
       </c>
     </row>
   </sheetData>
